--- a/HC_Carteras_propias.xlsx
+++ b/HC_Carteras_propias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814C4A94-2EB8-8B4D-9B81-C2F6577B5A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD07E2E7-10AD-C540-BDE5-620BDE04D51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16100" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{CE3D1765-37E3-48B3-B4D2-FF6910995400}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
   <si>
     <t>Documento</t>
   </si>
@@ -455,6 +455,12 @@
   </si>
   <si>
     <t>007850201</t>
+  </si>
+  <si>
+    <t>Laura Stefany Henao Cardenas</t>
+  </si>
+  <si>
+    <t>1026298117</t>
   </si>
 </sst>
 </file>
@@ -525,7 +531,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -536,6 +542,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -546,7 +553,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -556,7 +563,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -1550,36 +1557,44 @@
         <v>69</v>
       </c>
     </row>
+    <row r="70" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
+      <c r="A77" s="4" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B59" xr:uid="{67628BB9-8091-4766-8102-51505102CCD5}"/>
+  <conditionalFormatting sqref="A2:A70">
+    <cfRule type="duplicateValues" dxfId="11" priority="38"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:A15">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:A39">
-    <cfRule type="duplicateValues" dxfId="4" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25:A39">
-    <cfRule type="duplicateValues" dxfId="3" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A40:A69">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A69">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  <conditionalFormatting sqref="A40:A70">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
